--- a/artfynd/A 27244-2024 artfynd.xlsx
+++ b/artfynd/A 27244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60387973</v>
+        <v>90454856</v>
       </c>
       <c r="B2" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222056</v>
+        <v>4191</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Toarpsskogen, Sk</t>
+          <t>Toarp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382312.3947440585</v>
+        <v>382400</v>
       </c>
       <c r="R2" t="n">
-        <v>6156509.908651981</v>
+        <v>6156412</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-02</t>
+          <t>2021-01-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-02</t>
+          <t>2021-01-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,75 +775,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Karlsson</t>
+          <t>Lotta Strand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Karlsson</t>
+          <t>Lotta Strand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64934197</v>
+        <v>85034347</v>
       </c>
       <c r="B3" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222776</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Toarpsskogen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382326.017516911</v>
+        <v>382326</v>
       </c>
       <c r="R3" t="n">
-        <v>6156298.997279614</v>
+        <v>6156299</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,65 +903,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85034347</v>
+        <v>60387973</v>
       </c>
       <c r="B4" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>222056</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stor häxört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Circaea lutetiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Toarpsskogen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382326.017516911</v>
+        <v>382312</v>
       </c>
       <c r="R4" t="n">
-        <v>6156298.997279614</v>
+        <v>6156510</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,22 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-05-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,6 +1004,215 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64934197</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Toarpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>382326</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6156299</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Törringe</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-04-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-04-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131617646</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Toarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>382322</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6156548</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Törringe</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27244-2024 artfynd.xlsx
+++ b/artfynd/A 27244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90454856</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85034347</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60387973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64934197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,8 +1238,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>